--- a/r4-ELGA-e-Diagnose-4-lesende-zugriffe-get-vs-operation/StructureDefinition-at-elga-ediag-procedure.xlsx
+++ b/r4-ELGA-e-Diagnose-4-lesende-zugriffe-get-vs-operation/StructureDefinition-at-elga-ediag-procedure.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-31T06:56:37+00:00</t>
+    <t>2026-09-09T15:08:39+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -515,7 +515,7 @@
 </t>
   </si>
   <si>
-    <t>Zuordnung der Diagnose in einem internem Dokumentationssystem</t>
+    <t>Zuordnung der Diagnose in einem internen Dokumentationssystem.</t>
   </si>
   <si>
     <t>Business identifiers assigned to this procedure by the performer or other systems which remain constant as the resource is updated and is propagated from server to server.</t>
@@ -546,7 +546,7 @@
 </t>
   </si>
   <si>
-    <t>Verweis auf eine standardisierte FHIR-Ressource, ein Template oder einen Leitfaden, der beschreibt, wie die Prozedur durchgeführt werden soll</t>
+    <t>Verweis auf eine standardisierte FHIR-Ressource, ein Template oder einen Leitfaden, der beschreibt, wie die Prozedur durchgeführt werden soll.</t>
   </si>
   <si>
     <t>The URL pointing to a FHIR-defined protocol, guideline, order set or other definition that is adhered to in whole or in part by this Procedure.</t>
@@ -561,7 +561,7 @@
     <t>Procedure.instantiatesUri</t>
   </si>
   <si>
-    <t>Verweis auf ein externes Dokument</t>
+    <t>Verweis auf ein externes Dokument.</t>
   </si>
   <si>
     <t>The URL pointing to an externally maintained protocol, guideline, order set or other definition that is adhered to in whole or in part by this Procedure.</t>
@@ -584,7 +584,7 @@
 </t>
   </si>
   <si>
-    <t>Verweis auf eine Anforderung</t>
+    <t>Verweis auf eine Anforderung.</t>
   </si>
   <si>
     <t>A reference to a resource that contains details of the request for this procedure.</t>
@@ -607,7 +607,7 @@
 </t>
   </si>
   <si>
-    <t>Verweis der Ressource auf eine andere, übergreordnete Ressource</t>
+    <t>Verweis der Ressource auf eine andere, übergeordnete Ressource.</t>
   </si>
   <si>
     <t>A larger event of which this particular procedure is a component or step.</t>
@@ -625,7 +625,7 @@
     <t>Procedure.status</t>
   </si>
   <si>
-    <t>Nur tatsächlich durchgeführte (completed) oder irrtümlich dokumentierte (entered-in-error) Prozeduren</t>
+    <t>Nur tatsächlich durchgeführte (completed) oder irrtümlich dokumentierte (entered-in-error) Prozeduren.</t>
   </si>
   <si>
     <t>A code specifying the state of the procedure. Generally, this will be the in-progress or completed state.</t>
@@ -661,7 +661,7 @@
 </t>
   </si>
   <si>
-    <t>ToDo: Korrekturvermerk wird von digimed übernommen, ist noch in Abstimmung</t>
+    <t>ToDo: Korrekturvermerk wird von digimed übernommen, ist noch in Abstimmung.</t>
   </si>
   <si>
     <t>Captures the reason for the current state of the procedure.</t>
@@ -688,7 +688,7 @@
     <t>Procedure.category</t>
   </si>
   <si>
-    <t>Kategorisierung nach Verfahren</t>
+    <t>Kategorisierung nach Verfahren.</t>
   </si>
   <si>
     <t>A code that classifies the procedure for searching, sorting and display purposes (e.g. "Surgical Procedure").</t>
@@ -713,7 +713,7 @@
 </t>
   </si>
   <si>
-    <t>Prozedurencode der durchgeführten Prozedur</t>
+    <t>Prozedurencode der durchgeführten Prozedur.</t>
   </si>
   <si>
     <t>The specific procedure that is performed. Use text if the exact nature of the procedure cannot be coded (e.g. "Laparoscopic Appendectomy").</t>
@@ -834,7 +834,7 @@
 </t>
   </si>
   <si>
-    <t>Person, auf die sich die Prozedur bezieht</t>
+    <t>Person, auf die sich die Prozedur bezieht.</t>
   </si>
   <si>
     <t>The person, animal or group on which the procedure was performed.</t>
@@ -859,7 +859,7 @@
 </t>
   </si>
   <si>
-    <t>Behandlungskontakt</t>
+    <t>Behandlungskontakt.</t>
   </si>
   <si>
     <t>The Encounter during which this Procedure was created or performed or to which the creation of this record is tightly associated.</t>
@@ -887,7 +887,7 @@
 </t>
   </si>
   <si>
-    <t>Zeitpunkt der Durchführung</t>
+    <t>Zeitpunkt der Durchführung.</t>
   </si>
   <si>
     <t>Estimated or actual date, date-time, period, or age when the procedure was performed.  Allows a period to support complex procedures that span more than one date, and also allows for the length of the procedure to be captured.</t>
@@ -915,7 +915,7 @@
 </t>
   </si>
   <si>
-    <t>Gesundheitsdiensteanbieter, der die Prozedur eingetragen/dokumentiert hat</t>
+    <t>GDA, der die Prozedur eingetragen bzw. dokumentiert hat.</t>
   </si>
   <si>
     <t>Individual who recorded the record and takes responsibility for its content.</t>
@@ -934,7 +934,7 @@
 </t>
   </si>
   <si>
-    <t>Quelle der Information zur Prozedur (z. B. behandelnde Person, Patient oder Dritter)</t>
+    <t>Quelle der Information zur Prozedur (z. B. behandelnde Person, Patient oder Dritter).</t>
   </si>
   <si>
     <t>Individual who is making the procedure statement.</t>
@@ -953,7 +953,7 @@
 </t>
   </si>
   <si>
-    <t>Diese Person hat die Prozedur durchgeführt</t>
+    <t>Person, die die Prozedur durchgeführt hat.</t>
   </si>
   <si>
     <t>Limited to "real" people rather than equipment.</t>
@@ -1069,7 +1069,7 @@
 </t>
   </si>
   <si>
-    <t>Durchführungsort</t>
+    <t>Durchführungsort.</t>
   </si>
   <si>
     <t>The location where the procedure actually happened.  E.g. a newborn at home, a tracheostomy at a restaurant.</t>
@@ -1087,7 +1087,7 @@
     <t>Procedure.reasonCode</t>
   </si>
   <si>
-    <t>Code, des med. Grundes für die Durchführung der Prozedur</t>
+    <t>Code des medizinischen Grundes für die Durchführung der Prozedur.</t>
   </si>
   <si>
     <t>The coded reason why the procedure was performed. This may be a coded entity of some type, or may simply be present as text.</t>
@@ -1118,7 +1118,7 @@
 </t>
   </si>
   <si>
-    <t>Begründung dass die Prozedur durchgeführt worden ist - Verweis auf eine andere R. wie Condition, Observation,...</t>
+    <t>Begründung für die Durchführung der Prozedur; Verweis auf eine andere Ressource wie z.B. Condition oder Observation.</t>
   </si>
   <si>
     <t>The justification of why the procedure was performed.</t>
@@ -1134,7 +1134,7 @@
     <t>Procedure.bodySite</t>
   </si>
   <si>
-    <t>Betroffene Körperstelle</t>
+    <t>Betroffene Körperstelle.</t>
   </si>
   <si>
     <t>Detailed and structured anatomical location information. Multiple locations are allowed - e.g. multiple punch biopsies of a lesion.</t>
@@ -1158,7 +1158,7 @@
     <t>Procedure.outcome</t>
   </si>
   <si>
-    <t>Ergebnis der Prozedur</t>
+    <t>Ergebnis der Prozedur.</t>
   </si>
   <si>
     <t>The outcome of the procedure - did it resolve the reasons for the procedure being performed?</t>
@@ -1183,7 +1183,7 @@
 </t>
   </si>
   <si>
-    <t>Verweis auf ELGA-Befunde als medizinische Evidenz</t>
+    <t>Verweis auf ELGA-Befunde als medizinische Evidenz.</t>
   </si>
   <si>
     <t>This could be a histology result, pathology report, surgical report, etc.</t>
@@ -1198,7 +1198,7 @@
     <t>Procedure.complication</t>
   </si>
   <si>
-    <t>Komplikation/en während dem Eingriff</t>
+    <t>Komplikation während dem Eingriff.</t>
   </si>
   <si>
     <t>Any complications that occurred during the procedure, or in the immediate post-performance period. These are generally tracked separately from the notes, which will typically describe the procedure itself rather than any 'post procedure' issues.</t>
@@ -1223,7 +1223,7 @@
 </t>
   </si>
   <si>
-    <t>Eine Diagnose die durch die durchgeführte Prozedur entstanden ist</t>
+    <t>Diagnose, die durch die durchgeführte Prozedur entstanden ist.</t>
   </si>
   <si>
     <t>Any complications that occurred during the procedure, or in the immediate post-performance period.</t>
@@ -1235,7 +1235,7 @@
     <t>Procedure.followUp</t>
   </si>
   <si>
-    <t>Nachkontrolle (Code)</t>
+    <t>Nachkontrolle (Code).</t>
   </si>
   <si>
     <t>If the procedure required specific follow up - e.g. removal of sutures. The follow up may be represented as a simple note or could potentially be more complex, in which case the CarePlan resource can be used.</t>
@@ -1257,7 +1257,7 @@
 </t>
   </si>
   <si>
-    <t>Freitext zur Prozedur für Zusatzinformation</t>
+    <t>Freitext zur Prozedur als Zusatzinformation.</t>
   </si>
   <si>
     <t>Any other notes and comments about the procedure.</t>
@@ -1337,7 +1337,7 @@
     <t>Procedure.focalDevice</t>
   </si>
   <si>
-    <t>Prozedurendurchführendes Gerät</t>
+    <t>Gerät, das zur Durchführung der Prozedur verwendet wurde.</t>
   </si>
   <si>
     <t>A device that is implanted, removed or otherwise manipulated (calibration, battery replacement, fitting a prosthesis, attaching a wound-vac, etc.) as a focal portion of the Procedure.</t>
@@ -1396,7 +1396,7 @@
 </t>
   </si>
   <si>
-    <t>Verweis auf verwendete Materialien während der Prozedur (z.b. Medikamente)</t>
+    <t>Verweis auf während der Prozedur verwendete Materialien, z. B. Medikamente.</t>
   </si>
   <si>
     <t>Identifies medications, devices and any other substance used as part of the procedure.</t>
@@ -1415,7 +1415,7 @@
     <t>Procedure.usedCode</t>
   </si>
   <si>
-    <t>Code der Materialien, die während der Prozedur verwendetet wurden</t>
+    <t>Code der während der Prozedur verwendeten Materialien.</t>
   </si>
   <si>
     <t>Identifies coded items that were used as part of the procedure.</t>
